--- a/Updated Mapping Table.xlsx
+++ b/Updated Mapping Table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1939"/>
+  <dimension ref="A1:J1948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,11 @@
           <t>Cup Crawfish Pepperjack (Pick 3 Entree)</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cup Pepper Jack&amp;Crawfish</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>* Consolidated  Soups</t>
@@ -713,7 +718,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bowl Broccoli Cheese</t>
+          <t>Bowl Broccoli&amp;Cheese</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1547,7 +1552,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bowl PepperJack&amp;Crawfish</t>
+          <t>Bowl Pepper Jack&amp;Crawfish</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1593,7 +1598,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bowl PepperJack&amp;Crawfish</t>
+          <t>Bowl Pepper Jack&amp;Crawfish</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1971,7 +1976,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cup Broccoli Cheese</t>
+          <t>Cup Signature Beef Chili</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2001,7 +2006,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cup Broccoli&amp;Cheese</t>
+          <t>Cup Broccoli Cheese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2299,7 +2304,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cup Broccoli&amp;Cheese</t>
+          <t>Cup Broccoli Cheese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -46470,7 +46475,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>Spicy Chicken Pizza</t>
+          <t>Spicy Shrimp Pizza</t>
         </is>
       </c>
       <c r="F1399" t="inlineStr">
@@ -52285,7 +52290,7 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>Half Strawberry Fields</t>
+          <t>Half Taco Salad</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
@@ -53982,7 +53987,7 @@
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>French Dip</t>
+          <t>1/2 French Dip</t>
         </is>
       </c>
       <c r="F1578" t="inlineStr">
@@ -54012,7 +54017,7 @@
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>Half Tenderloin Steak</t>
+          <t>1/2 Grilled Steak Sand</t>
         </is>
       </c>
       <c r="F1579" t="inlineStr">
@@ -55963,7 +55968,7 @@
       </c>
       <c r="E1636" t="inlineStr">
         <is>
-          <t>1/2 Newk's Q</t>
+          <t>1/2 Newks Philly</t>
         </is>
       </c>
       <c r="F1636" t="inlineStr">
@@ -55989,7 +55994,7 @@
       </c>
       <c r="E1637" t="inlineStr">
         <is>
-          <t>1/2 Newk's Q</t>
+          <t>1/2 Newks Philly</t>
         </is>
       </c>
       <c r="F1637" t="inlineStr">
@@ -57621,7 +57626,7 @@
       </c>
       <c r="E1685" t="inlineStr">
         <is>
-          <t>1/2 Turkey Avo</t>
+          <t>1/2 Turkey Brst</t>
         </is>
       </c>
       <c r="F1685" t="inlineStr">
@@ -57799,7 +57804,7 @@
       </c>
       <c r="E1690" t="inlineStr">
         <is>
-          <t>1/2 Turkey Brst</t>
+          <t>1/2 Turkey Avo</t>
         </is>
       </c>
       <c r="F1690" t="inlineStr">
@@ -57825,7 +57830,7 @@
       </c>
       <c r="E1691" t="inlineStr">
         <is>
-          <t>1/2 Turkey Brst</t>
+          <t>1/2 Turkey Avo</t>
         </is>
       </c>
       <c r="F1691" t="inlineStr">
@@ -67017,7 +67022,7 @@
       </c>
       <c r="E1915" t="inlineStr">
         <is>
-          <t>Chkn Salad Wrap</t>
+          <t>Chicken Salad Wrap</t>
         </is>
       </c>
       <c r="F1915" t="inlineStr">
@@ -67063,7 +67068,7 @@
       </c>
       <c r="E1916" t="inlineStr">
         <is>
-          <t>Chkn Salad Wrap</t>
+          <t>Chicken Salad Wrap</t>
         </is>
       </c>
       <c r="F1916" t="inlineStr">
@@ -68031,6 +68036,291 @@
       <c r="J1939" t="inlineStr">
         <is>
           <t>EE 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="C1940" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>Cup Broccoli (Entree)</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>Cup Broccoli Cheese</t>
+        </is>
+      </c>
+      <c r="F1940" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+      <c r="H1940" t="inlineStr">
+        <is>
+          <t>SoupBroccoliCheese, * Consolidated  Soups, Guest Count 1, EE .5</t>
+        </is>
+      </c>
+      <c r="I1940" t="inlineStr">
+        <is>
+          <t>Guest Count 1</t>
+        </is>
+      </c>
+      <c r="J1940" t="inlineStr">
+        <is>
+          <t>EE .5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="C1941" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>Cup Broccoli (Half Pairing Entree)</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>Cup Broccoli Cheese</t>
+        </is>
+      </c>
+      <c r="F1941" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+      <c r="H1941" t="inlineStr">
+        <is>
+          <t>SoupBroccoliCheese, * Consolidated  Soups, Guest Count 0.5, EE .5</t>
+        </is>
+      </c>
+      <c r="I1941" t="inlineStr">
+        <is>
+          <t>Guest Count 0.5</t>
+        </is>
+      </c>
+      <c r="J1941" t="inlineStr">
+        <is>
+          <t>EE .5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="C1942" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>Cup Broccoli (Pick 3 Entree)</t>
+        </is>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>Cup Broccoli Cheese</t>
+        </is>
+      </c>
+      <c r="F1942" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+      <c r="H1942" t="inlineStr">
+        <is>
+          <t>SoupBroccoliCheese, * Consolidated  Soups, Guest Count 0.5, EE .5</t>
+        </is>
+      </c>
+      <c r="I1942" t="inlineStr">
+        <is>
+          <t>Guest Count 0.5</t>
+        </is>
+      </c>
+      <c r="J1942" t="inlineStr">
+        <is>
+          <t>EE .5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="C1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>Cup Broccoli (Full Pairing Entree)</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>Cup Broccoli Cheese</t>
+        </is>
+      </c>
+      <c r="F1943" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+      <c r="H1943" t="inlineStr">
+        <is>
+          <t>SoupBroccoliCheese, * Consolidated  Soups, Guest Count 0.5, EE .5</t>
+        </is>
+      </c>
+      <c r="I1943" t="inlineStr">
+        <is>
+          <t>Guest Count 0.5</t>
+        </is>
+      </c>
+      <c r="J1943" t="inlineStr">
+        <is>
+          <t>EE .5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="C1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>Cup Broccoli (POS Pairing Choice)</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>Cup Broccoli Cheese</t>
+        </is>
+      </c>
+      <c r="F1944" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="C1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli (Entree)</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli&amp;Cheese</t>
+        </is>
+      </c>
+      <c r="F1945" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+      <c r="H1945" t="inlineStr">
+        <is>
+          <t>SoupBroccoliCheese, * Consolidated  Soups, Guest Count 1, EE 1</t>
+        </is>
+      </c>
+      <c r="I1945" t="inlineStr">
+        <is>
+          <t>Guest Count 1</t>
+        </is>
+      </c>
+      <c r="J1945" t="inlineStr">
+        <is>
+          <t>EE 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="C1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli (OLO Entree)</t>
+        </is>
+      </c>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli&amp;Cheese</t>
+        </is>
+      </c>
+      <c r="F1946" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+      <c r="H1946" t="inlineStr">
+        <is>
+          <t>SoupBroccoliCheese, * Consolidated  Soups, Guest Count 1, EE 1</t>
+        </is>
+      </c>
+      <c r="I1946" t="inlineStr">
+        <is>
+          <t>Guest Count 1</t>
+        </is>
+      </c>
+      <c r="J1946" t="inlineStr">
+        <is>
+          <t>EE 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="C1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli (Full Pairing Entree)</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli&amp;Cheese</t>
+        </is>
+      </c>
+      <c r="F1947" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
+        </is>
+      </c>
+      <c r="H1947" t="inlineStr">
+        <is>
+          <t>SoupBroccoliCheese, * Consolidated  Soups, Guest Count 0.5, EE 1</t>
+        </is>
+      </c>
+      <c r="I1947" t="inlineStr">
+        <is>
+          <t>Guest Count 0.5</t>
+        </is>
+      </c>
+      <c r="J1947" t="inlineStr">
+        <is>
+          <t>EE 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="C1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli (OLO Pairing Choice)</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>Bowl Broccoli&amp;Cheese</t>
+        </is>
+      </c>
+      <c r="F1948" t="inlineStr">
+        <is>
+          <t>* Consolidated  Soups</t>
         </is>
       </c>
     </row>

--- a/Updated Mapping Table.xlsx
+++ b/Updated Mapping Table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1948"/>
+  <dimension ref="A1:J1949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68324,6 +68324,49 @@
         </is>
       </c>
     </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>1100000011410021019</t>
+        </is>
+      </c>
+      <c r="B1949" t="n">
+        <v>40070119</v>
+      </c>
+      <c r="C1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>Asian Chkn Sal</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>Asian Chicken Salad (OLO Pairing Choice)</t>
+        </is>
+      </c>
+      <c r="F1949" t="inlineStr">
+        <is>
+          <t>* Consolidated Salads</t>
+        </is>
+      </c>
+      <c r="G1949" t="inlineStr">
+        <is>
+          <t>b89eaa33-7c46-4b86-a10e-7e8528d6220f</t>
+        </is>
+      </c>
+      <c r="H1949" t="inlineStr">
+        <is>
+          <t>ChickenAsianSalad, Guest Count 0.5, * Consolidated Salads</t>
+        </is>
+      </c>
+      <c r="I1949" t="inlineStr">
+        <is>
+          <t>Guest Count 0.5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
